--- a/토요타_models.xlsx
+++ b/토요타_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'토요타 트랜스폰더 DB'!$A$1:$P$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'토요타 트랜스폰더 DB'!$A$1:$P$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P121"/>
+  <dimension ref="A1:P113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -655,14 +655,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>ID72(TMS37126)</t>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)[스마트키], ID72[일반 키]</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I2" s="9" t="inlineStr"/>
@@ -674,21 +674,17 @@
       <c r="K2" s="9" t="inlineStr"/>
       <c r="L2" s="9" t="inlineStr"/>
       <c r="M2" s="9" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O2" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius c·Aqua 2012–2015 Texas G DST80 스마트키, 89904-0E091·89904-47370(주파수 미표기라 뺌)), 위키백과(프리우스 C 2018.5.14 국내 판매 시작 후 판매 부진으로 수입 중단), CEO스코어데일리(2019.2 프리우스C 판매 정리)</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t>2016년 이후 생산분 칩 자료 없음 — 2012~2015 G 칩 기준 추정</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius c·Aqua 2012–2015 Texas G DST80 스마트키, 89904-0E091·89904-47370(주파수 미표기라 뺌)), 위키백과(프리우스 C 2018.5.14 국내 판매 시작 후 판매 부진으로 수입 중단), CEO스코어데일리(2019.2 프리우스C 판매 정리), programautokeys·toyotapartsdeal(2012~2022 Prius c 리모컨 일체형 키 89070-52F60 HYQ12BDM G 칩 — 2018년식도 G 칩 계열, 북미형이라 품번 뺌)</t>
+        </is>
+      </c>
+      <c r="P2" s="9" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -721,14 +717,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID72(TMS37126)</t>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)[스마트키], ID72[일반 키]</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr"/>
@@ -740,21 +736,17 @@
       <c r="K3" s="9" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr"/>
       <c r="M3" s="9" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O3" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius c·Aqua 2012–2015 Texas G DST80 스마트키, 89904-0E091·89904-47370(주파수 미표기라 뺌)), 위키백과(프리우스 C 2018.5.14 국내 판매 시작 후 판매 부진으로 수입 중단), CEO스코어데일리(2019.2 프리우스C 판매 정리)</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>2016년 이후 생산분 칩 자료 없음 — 2012~2015 G 칩 기준 추정</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius c·Aqua 2012–2015 Texas G DST80 스마트키, 89904-0E091·89904-47370(주파수 미표기라 뺌)), 위키백과(프리우스 C 2018.5.14 국내 판매 시작 후 판매 부진으로 수입 중단), CEO스코어데일리(2019.2 프리우스C 판매 정리), programautokeys·toyotapartsdeal(2012~2022 Prius c 리모컨 일체형 키 89070-52F60 HYQ12BDM G 칩 — 2018년식도 G 칩 계열, 북미형이라 품번 뺌)</t>
+        </is>
+      </c>
+      <c r="P3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -954,22 +946,22 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>코롤라 (E210, 12세대)</t>
+          <t>프리우스 (XW30, 3세대)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -977,9 +969,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M)</t>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -989,32 +981,32 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr"/>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K7" s="9" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>8990H-02050[해외 공용 품번]</t>
+          <t>89904-47190[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Corolla E210 2018–2021 NXP HITAG-AES 4A-AA(8990H-02030 314MHz 뺌), 비상키 69515-33100), auto-keys.eu(순정 Corolla 8990H-02050 434MHz NCF29A1M), 위키백과(E140 이후 코롤라 국내 미수입)</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -1024,22 +1016,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>코롤라 (E210, 12세대)</t>
+          <t>프리우스 (XW30, 3세대)</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1047,9 +1039,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M)</t>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -1059,32 +1051,32 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr"/>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K8" s="9" t="inlineStr"/>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>8990H-02050[해외 공용 품번]</t>
+          <t>89904-47190[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Corolla E210 2018–2021 NXP HITAG-AES 4A-AA(8990H-02030 314MHz 뺌), 비상키 69515-33100), auto-keys.eu(순정 Corolla 8990H-02050 434MHz NCF29A1M), 위키백과(E140 이후 코롤라 국내 미수입)</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -1094,22 +1086,22 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>코롤라 (E210, 12세대)</t>
+          <t>프리우스 (XW30, 3세대)</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1117,9 +1109,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M)</t>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1129,32 +1121,32 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr"/>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K9" s="9" t="inlineStr"/>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>8990H-02050[해외 공용 품번]</t>
+          <t>89904-47190[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O9" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Corolla E210 2018–2021 NXP HITAG-AES 4A-AA(8990H-02030 314MHz 뺌), 비상키 69515-33100), auto-keys.eu(순정 Corolla 8990H-02050 434MHz NCF29A1M), 위키백과(E140 이후 코롤라 국내 미수입)</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -1164,22 +1156,22 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>코롤라 (E210, 12세대)</t>
+          <t>프리우스 (XW30, 3세대)</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1187,9 +1179,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M)</t>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1199,32 +1191,32 @@
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr"/>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K10" s="9" t="inlineStr"/>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>8990H-02050[해외 공용 품번]</t>
+          <t>89904-47190[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Corolla E210 2018–2021 NXP HITAG-AES 4A-AA(8990H-02030 314MHz 뺌), 비상키 69515-33100), auto-keys.eu(순정 Corolla 8990H-02050 434MHz NCF29A1M), 위키백과(E140 이후 코롤라 국내 미수입)</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1234,22 +1226,22 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>코롤라 (E210, 12세대)</t>
+          <t>프리우스 (XW30, 3세대)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1257,9 +1249,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M)</t>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -1269,32 +1261,32 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr"/>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K11" s="9" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>8990H-02050[해외 공용 품번]</t>
+          <t>89904-47190[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O11" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Corolla E210 2018–2021 NXP HITAG-AES 4A-AA(8990H-02030 314MHz 뺌), 비상키 69515-33100), auto-keys.eu(순정 Corolla 8990H-02050 434MHz NCF29A1M), 위키백과(E140 이후 코롤라 국내 미수입)</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -1304,22 +1296,22 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>코롤라 (E210, 12세대)</t>
+          <t>프리우스 (XW30, 3세대)</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1327,9 +1319,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M)</t>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -1339,32 +1331,32 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr"/>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K12" s="9" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>8990H-02441[해외 공용 품번], 8990H-02420[해외 공용 품번]</t>
+          <t>89904-47190[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Corolla E210 Facelift 2024–2026 HITAG-AES 4A-BA, 비상키 69515-K0020), auto-keys.eu(순정 Corolla 2024+ 8990H-02441·8990H-02420 433MHz HITAG AES)</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1374,22 +1366,22 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>코롤라 (E210, 12세대)</t>
+          <t>프리우스 (XW30, 3세대)</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2015(단종)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1397,9 +1389,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M)</t>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -1409,32 +1401,32 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr"/>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K13" s="9" t="inlineStr"/>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>8990H-02441[해외 공용 품번], 8990H-02420[해외 공용 품번]</t>
+          <t>89904-47190[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O13" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Corolla E210 Facelift 2024–2026 HITAG-AES 4A-BA, 비상키 69515-K0020), auto-keys.eu(순정 Corolla 2024+ 8990H-02441·8990H-02420 433MHz HITAG AES)</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -1444,12 +1436,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>코롤라 (E210, 12세대)</t>
+          <t>프리우스 (XW50, 4세대)</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1467,9 +1459,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M)</t>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -1479,32 +1471,32 @@
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr"/>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>TOY51</t>
+        </is>
+      </c>
       <c r="K14" s="9" t="inlineStr"/>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>8990H-02441[해외 공용 품번], 8990H-02420[해외 공용 품번]</t>
+          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Corolla E210 Facelift 2024–2026 HITAG-AES 4A-BA, 비상키 69515-K0020), auto-keys.eu(순정 Corolla 2024+ 8990H-02441·8990H-02420 433MHz HITAG AES)</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -1514,22 +1506,22 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW30, 3세대)</t>
+          <t>프리우스 (XW50, 4세대)</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1539,7 +1531,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -1549,18 +1541,18 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>89904-47190[해외 공용 품번]</t>
+          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr"/>
@@ -1571,7 +1563,7 @@
       </c>
       <c r="O15" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr"/>
@@ -1584,22 +1576,22 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW30, 3세대)</t>
+          <t>프리우스 (XW50, 4세대)</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1609,7 +1601,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1619,18 +1611,18 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr"/>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>89904-47190[해외 공용 품번]</t>
+          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr"/>
@@ -1641,7 +1633,7 @@
       </c>
       <c r="O16" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
         </is>
       </c>
       <c r="P16" s="9" t="inlineStr"/>
@@ -1654,22 +1646,22 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW30, 3세대)</t>
+          <t>프리우스 (XW50, 4세대)</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1679,7 +1671,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -1689,18 +1681,18 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr"/>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>89904-47190[해외 공용 품번]</t>
+          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr"/>
@@ -1711,7 +1703,7 @@
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr"/>
@@ -1724,22 +1716,22 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW30, 3세대)</t>
+          <t>프리우스 (XW50, 4세대)</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1749,7 +1741,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -1759,18 +1751,18 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr"/>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>89904-47190[해외 공용 품번]</t>
+          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr"/>
@@ -1781,7 +1773,7 @@
       </c>
       <c r="O18" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
         </is>
       </c>
       <c r="P18" s="9" t="inlineStr"/>
@@ -1794,22 +1786,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW30, 3세대)</t>
+          <t>프리우스 (XW50, 4세대)</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1819,7 +1811,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -1829,18 +1821,18 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>89904-47190[해외 공용 품번]</t>
+          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr"/>
@@ -1851,7 +1843,7 @@
       </c>
       <c r="O19" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
         </is>
       </c>
       <c r="P19" s="9" t="inlineStr"/>
@@ -1864,22 +1856,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW30, 3세대)</t>
+          <t>프리우스 (XW50, 4세대)</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1889,7 +1881,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -1899,18 +1891,18 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr"/>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>89904-47190[해외 공용 품번]</t>
+          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr"/>
@@ -1921,7 +1913,7 @@
       </c>
       <c r="O20" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
         </is>
       </c>
       <c r="P20" s="9" t="inlineStr"/>
@@ -1934,22 +1926,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW30, 3세대)</t>
+          <t>프리우스 (XW50, 4세대)</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>2015(단종)</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023(단종)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1959,7 +1951,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -1969,18 +1961,18 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>89904-47190[해외 공용 품번]</t>
+          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr"/>
@@ -1991,7 +1983,7 @@
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius Smart Key 2010–2015 Texas G DST80(89904-47150 315MHz 뺌), 비상키 69515-52120), abkeys(Prius 2009-2015 유럽 89904-47190 433MHz B74EA P1 98), 위키백과(3세대 2009.10 국내 출시, 4세대 2016.3)</t>
+          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
         </is>
       </c>
       <c r="P21" s="9" t="inlineStr"/>
@@ -2004,12 +1996,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW50, 4세대)</t>
+          <t>프리우스 (XW60, 5세대)</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2039,7 +2031,7 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -2048,11 +2040,7 @@
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr"/>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L22" s="9" t="inlineStr"/>
       <c r="M22" s="9" t="inlineStr"/>
       <c r="N22" s="9" t="inlineStr">
         <is>
@@ -2061,7 +2049,7 @@
       </c>
       <c r="O22" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
+          <t>transpondery(Toyota Prius WX60 2022–2026 Texas H-8A DST-AES 8A-BA(8990H-47120·47130 315MHz 뺌), 비상키 69515-K0020), 위키백과(5세대 2023.12.13 국내 출시)</t>
         </is>
       </c>
       <c r="P22" s="9" t="inlineStr"/>
@@ -2074,12 +2062,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW50, 4세대)</t>
+          <t>프리우스 (XW60, 5세대)</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2109,7 +2097,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
@@ -2118,11 +2106,7 @@
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr"/>
-      <c r="L23" s="9" t="inlineStr">
-        <is>
-          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L23" s="9" t="inlineStr"/>
       <c r="M23" s="9" t="inlineStr"/>
       <c r="N23" s="9" t="inlineStr">
         <is>
@@ -2131,7 +2115,7 @@
       </c>
       <c r="O23" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
+          <t>transpondery(Toyota Prius WX60 2022–2026 Texas H-8A DST-AES 8A-BA(8990H-47120·47130 315MHz 뺌), 비상키 69515-K0020), 위키백과(5세대 2023.12.13 국내 출시)</t>
         </is>
       </c>
       <c r="P23" s="9" t="inlineStr"/>
@@ -2144,12 +2128,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW50, 4세대)</t>
+          <t>프리우스 (XW60, 5세대)</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2179,7 +2163,7 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
@@ -2188,11 +2172,7 @@
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr"/>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L24" s="9" t="inlineStr"/>
       <c r="M24" s="9" t="inlineStr"/>
       <c r="N24" s="9" t="inlineStr">
         <is>
@@ -2201,7 +2181,7 @@
       </c>
       <c r="O24" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
+          <t>transpondery(Toyota Prius WX60 2022–2026 Texas H-8A DST-AES 8A-BA(8990H-47120·47130 315MHz 뺌), 비상키 69515-K0020), 위키백과(5세대 2023.12.13 국내 출시)</t>
         </is>
       </c>
       <c r="P24" s="9" t="inlineStr"/>
@@ -2214,12 +2194,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW50, 4세대)</t>
+          <t>프리우스 (XW60, 5세대)</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2249,7 +2229,7 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
@@ -2258,11 +2238,7 @@
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr"/>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L25" s="9" t="inlineStr"/>
       <c r="M25" s="9" t="inlineStr"/>
       <c r="N25" s="9" t="inlineStr">
         <is>
@@ -2271,7 +2247,7 @@
       </c>
       <c r="O25" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
+          <t>transpondery(Toyota Prius WX60 2022–2026 Texas H-8A DST-AES 8A-BA(8990H-47120·47130 315MHz 뺌), 비상키 69515-K0020), 위키백과(5세대 2023.12.13 국내 출시)</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr"/>
@@ -2284,22 +2260,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW50, 4세대)</t>
+          <t>캠리 (XV40, 6세대 후기형)</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -2309,7 +2285,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID67(TMS37126)</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -2319,29 +2295,29 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
+          <t>89904-33100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr"/>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>스마트키 ECU(93C86)</t>
         </is>
       </c>
       <c r="O26" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
+          <t>transpondery(Toyota Camry 2005–2010 Texas Crypto 4D ID67·ID68, Smart Key 2007–2010 DST40 Page1 94(89904-06041 315MHz 뺌), TOY48 비상키 69515-52120), abkeys(Aurion·Camry 2007-2010 유럽·중동 스마트키 89904-33100 433MHz B53EA P1 D4), 위키백과(2009.10.20 한국토요타 공식 판매 — 일본산), 이투데이(캠리 3490만원)</t>
         </is>
       </c>
       <c r="P26" s="9" t="inlineStr"/>
@@ -2354,22 +2330,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW50, 4세대)</t>
+          <t>캠리 (XV40, 6세대 후기형)</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -2379,7 +2355,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID67(TMS37126)</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -2389,29 +2365,29 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
+          <t>89904-33100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M27" s="9" t="inlineStr"/>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>스마트키 ECU(93C86)</t>
         </is>
       </c>
       <c r="O27" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
+          <t>transpondery(Toyota Camry 2005–2010 Texas Crypto 4D ID67·ID68, Smart Key 2007–2010 DST40 Page1 94(89904-06041 315MHz 뺌), TOY48 비상키 69515-52120), abkeys(Aurion·Camry 2007-2010 유럽·중동 스마트키 89904-33100 433MHz B53EA P1 D4), 위키백과(2009.10.20 한국토요타 공식 판매 — 일본산), 이투데이(캠리 3490만원)</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr"/>
@@ -2424,22 +2400,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW50, 4세대)</t>
+          <t>캠리 (XV40, 6세대 후기형)</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2011(단종)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -2449,7 +2425,7 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID67(TMS37126)</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -2459,29 +2435,29 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-52120[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr"/>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
+          <t>89904-33100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr"/>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>스마트키 ECU(93C86)</t>
         </is>
       </c>
       <c r="O28" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
+          <t>transpondery(Toyota Camry 2005–2010 Texas Crypto 4D ID67·ID68, Smart Key 2007–2010 DST40 Page1 94(89904-06041 315MHz 뺌), TOY48 비상키 69515-52120), abkeys(Aurion·Camry 2007-2010 유럽·중동 스마트키 89904-33100 433MHz B53EA P1 D4), 위키백과(2009.10.20 한국토요타 공식 판매 — 일본산), 이투데이(캠리 3490만원)</t>
         </is>
       </c>
       <c r="P28" s="9" t="inlineStr"/>
@@ -2494,12 +2470,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW50, 4세대)</t>
+          <t>캠리 (XV50, 7세대)</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>2023(단종)</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2529,7 +2505,7 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -2540,7 +2516,7 @@
       <c r="K29" s="9" t="inlineStr"/>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>89904-47560[해외 공용 품번], 89904-47561[해외 공용 품번]</t>
+          <t>89904-33460[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr"/>
@@ -2551,7 +2527,7 @@
       </c>
       <c r="O29" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius 2016–2022 Texas H-8A DST-AES A9(89904-47530 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Prius 2016-2018 유럽·중동 89904-47560·47561 433MHz BR1EW P1 A9), 위키백과(4세대 2016.3 국내 판매, 5세대 2023.12.13)</t>
+          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr"/>
@@ -2564,12 +2540,12 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW60, 5세대)</t>
+          <t>캠리 (XV50, 7세대)</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2599,7 +2575,7 @@
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -2608,7 +2584,11 @@
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr"/>
-      <c r="L30" s="9" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>89904-33460[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M30" s="9" t="inlineStr"/>
       <c r="N30" s="9" t="inlineStr">
         <is>
@@ -2617,7 +2597,7 @@
       </c>
       <c r="O30" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius WX60 2022–2026 Texas H-8A DST-AES 8A-BA(8990H-47120·47130 315MHz 뺌), 비상키 69515-K0020), 위키백과(5세대 2023.12.13 국내 출시)</t>
+          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
         </is>
       </c>
       <c r="P30" s="9" t="inlineStr"/>
@@ -2630,12 +2610,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW60, 5세대)</t>
+          <t>캠리 (XV50, 7세대)</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2665,7 +2645,7 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
@@ -2674,7 +2654,11 @@
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="9" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>89904-33460[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M31" s="9" t="inlineStr"/>
       <c r="N31" s="9" t="inlineStr">
         <is>
@@ -2683,7 +2667,7 @@
       </c>
       <c r="O31" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius WX60 2022–2026 Texas H-8A DST-AES 8A-BA(8990H-47120·47130 315MHz 뺌), 비상키 69515-K0020), 위키백과(5세대 2023.12.13 국내 출시)</t>
+          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr"/>
@@ -2696,12 +2680,12 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW60, 5세대)</t>
+          <t>캠리 (XV50, 7세대)</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2731,7 +2715,7 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
@@ -2740,7 +2724,11 @@
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr"/>
-      <c r="L32" s="9" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>89904-33460[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M32" s="9" t="inlineStr"/>
       <c r="N32" s="9" t="inlineStr">
         <is>
@@ -2749,7 +2737,7 @@
       </c>
       <c r="O32" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius WX60 2022–2026 Texas H-8A DST-AES 8A-BA(8990H-47120·47130 315MHz 뺌), 비상키 69515-K0020), 위키백과(5세대 2023.12.13 국내 출시)</t>
+          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
         </is>
       </c>
       <c r="P32" s="9" t="inlineStr"/>
@@ -2762,12 +2750,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>프리우스 (XW60, 5세대)</t>
+          <t>캠리 (XV50, 7세대)</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2797,7 +2785,7 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
@@ -2806,7 +2794,11 @@
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr"/>
-      <c r="L33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>89904-33460[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M33" s="9" t="inlineStr"/>
       <c r="N33" s="9" t="inlineStr">
         <is>
@@ -2815,7 +2807,7 @@
       </c>
       <c r="O33" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Prius WX60 2022–2026 Texas H-8A DST-AES 8A-BA(8990H-47120·47130 315MHz 뺌), 비상키 69515-K0020), 위키백과(5세대 2023.12.13 국내 출시)</t>
+          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
         </is>
       </c>
       <c r="P33" s="9" t="inlineStr"/>
@@ -2828,22 +2820,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV40, 6세대 후기형)</t>
+          <t>캠리 (XV50, 7세대)</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2017(단종)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -2853,7 +2845,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>ID67(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -2863,29 +2855,29 @@
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr"/>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>89904-33100[해외 공용 품번]</t>
+          <t>89904-33460[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M34" s="9" t="inlineStr"/>
       <c r="N34" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU(93C86)</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O34" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2005–2010 Texas Crypto 4D ID67·ID68, Smart Key 2007–2010 DST40 Page1 94(89904-06041 315MHz 뺌), TOY48 비상키 69515-52120), abkeys(Aurion·Camry 2007-2010 유럽·중동 스마트키 89904-33100 433MHz B53EA P1 D4), 위키백과(2009.10.20 한국토요타 공식 판매 — 일본산), 이투데이(캠리 3490만원)</t>
+          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
         </is>
       </c>
       <c r="P34" s="9" t="inlineStr"/>
@@ -2898,22 +2890,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV40, 6세대 후기형)</t>
+          <t>캠리 (XV70, 8세대)</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2923,7 +2915,7 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>ID67(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -2933,29 +2925,29 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr"/>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>89904-33100[해외 공용 품번]</t>
+          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr"/>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU(93C86)</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O35" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2005–2010 Texas Crypto 4D ID67·ID68, Smart Key 2007–2010 DST40 Page1 94(89904-06041 315MHz 뺌), TOY48 비상키 69515-52120), abkeys(Aurion·Camry 2007-2010 유럽·중동 스마트키 89904-33100 433MHz B53EA P1 D4), 위키백과(2009.10.20 한국토요타 공식 판매 — 일본산), 이투데이(캠리 3490만원)</t>
+          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
         </is>
       </c>
       <c r="P35" s="9" t="inlineStr"/>
@@ -2968,22 +2960,22 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV40, 6세대 후기형)</t>
+          <t>캠리 (XV70, 8세대)</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>2011(단종)</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -2993,7 +2985,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>ID67(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -3003,29 +2995,29 @@
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>69515-52120[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr"/>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>89904-33100[해외 공용 품번]</t>
+          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr"/>
       <c r="N36" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU(93C86)</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O36" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2005–2010 Texas Crypto 4D ID67·ID68, Smart Key 2007–2010 DST40 Page1 94(89904-06041 315MHz 뺌), TOY48 비상키 69515-52120), abkeys(Aurion·Camry 2007-2010 유럽·중동 스마트키 89904-33100 433MHz B53EA P1 D4), 위키백과(2009.10.20 한국토요타 공식 판매 — 일본산), 이투데이(캠리 3490만원)</t>
+          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
         </is>
       </c>
       <c r="P36" s="9" t="inlineStr"/>
@@ -3038,12 +3030,12 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV50, 7세대)</t>
+          <t>캠리 (XV70, 8세대)</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -3073,7 +3065,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -3084,7 +3076,7 @@
       <c r="K37" s="9" t="inlineStr"/>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>89904-33460[해외 공용 품번]</t>
+          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr"/>
@@ -3095,7 +3087,7 @@
       </c>
       <c r="O37" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
+          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
         </is>
       </c>
       <c r="P37" s="9" t="inlineStr"/>
@@ -3108,12 +3100,12 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV50, 7세대)</t>
+          <t>캠리 (XV70, 8세대)</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -3143,7 +3135,7 @@
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -3154,7 +3146,7 @@
       <c r="K38" s="9" t="inlineStr"/>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>89904-33460[해외 공용 품번]</t>
+          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr"/>
@@ -3165,7 +3157,7 @@
       </c>
       <c r="O38" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
+          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
         </is>
       </c>
       <c r="P38" s="9" t="inlineStr"/>
@@ -3178,12 +3170,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV50, 7세대)</t>
+          <t>캠리 (XV70, 8세대)</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -3213,7 +3205,7 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
@@ -3224,7 +3216,7 @@
       <c r="K39" s="9" t="inlineStr"/>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>89904-33460[해외 공용 품번]</t>
+          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M39" s="9" t="inlineStr"/>
@@ -3235,7 +3227,7 @@
       </c>
       <c r="O39" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
+          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
         </is>
       </c>
       <c r="P39" s="9" t="inlineStr"/>
@@ -3248,12 +3240,12 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV50, 7세대)</t>
+          <t>캠리 (XV70, 8세대)</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -3283,7 +3275,7 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
@@ -3294,7 +3286,7 @@
       <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>89904-33460[해외 공용 품번]</t>
+          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M40" s="9" t="inlineStr"/>
@@ -3305,7 +3297,7 @@
       </c>
       <c r="O40" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
+          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
         </is>
       </c>
       <c r="P40" s="9" t="inlineStr"/>
@@ -3318,12 +3310,12 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV50, 7세대)</t>
+          <t>캠리 (XV70, 8세대)</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -3353,7 +3345,7 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
@@ -3364,7 +3356,7 @@
       <c r="K41" s="9" t="inlineStr"/>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>89904-33460[해외 공용 품번]</t>
+          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr"/>
@@ -3375,7 +3367,7 @@
       </c>
       <c r="O41" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
+          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
         </is>
       </c>
       <c r="P41" s="9" t="inlineStr"/>
@@ -3388,12 +3380,12 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV50, 7세대)</t>
+          <t>캠리 (XV70, 8세대)</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>2017(단종)</t>
+          <t>2024(단종)</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -3423,7 +3415,7 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
@@ -3434,7 +3426,7 @@
       <c r="K42" s="9" t="inlineStr"/>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>89904-33460[해외 공용 품번]</t>
+          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M42" s="9" t="inlineStr"/>
@@ -3445,7 +3437,7 @@
       </c>
       <c r="O42" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry Smart Key 2012–2017 Texas H-8A DST-AES(89904-06140 314MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 Camry·Avalon·Aurion 2011+ 유럽·중동 스마트키 89904-33460 433MHz BA4EQ P1 88), 위키백과(미국산 7세대 2012.1 국내 출시, 2013 대한민국 올해의 차, 8세대 2017.10.19)</t>
+          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
         </is>
       </c>
       <c r="P42" s="9" t="inlineStr"/>
@@ -3458,12 +3450,12 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV70, 8세대)</t>
+          <t>캠리 (XV80, 9세대)</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3483,7 +3475,7 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -3493,7 +3485,7 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
@@ -3502,11 +3494,7 @@
         </is>
       </c>
       <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L43" s="9" t="inlineStr"/>
       <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="9" t="inlineStr">
         <is>
@@ -3515,7 +3503,7 @@
       </c>
       <c r="O43" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
+          <t>transpondery(Toyota Camry 80 2025–2026 North America NXP HITAG-AES ID4A NCF29A1M(8990H-AQ010 314MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(9세대 2024.11.26 국내 출시)</t>
         </is>
       </c>
       <c r="P43" s="9" t="inlineStr"/>
@@ -3528,12 +3516,12 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV70, 8세대)</t>
+          <t>캠리 (XV80, 9세대)</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3553,7 +3541,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
@@ -3563,7 +3551,7 @@
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -3572,11 +3560,7 @@
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr">
-        <is>
-          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L44" s="9" t="inlineStr"/>
       <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="9" t="inlineStr">
         <is>
@@ -3585,7 +3569,7 @@
       </c>
       <c r="O44" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
+          <t>transpondery(Toyota Camry 80 2025–2026 North America NXP HITAG-AES ID4A NCF29A1M(8990H-AQ010 314MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(9세대 2024.11.26 국내 출시)</t>
         </is>
       </c>
       <c r="P44" s="9" t="inlineStr"/>
@@ -3598,12 +3582,12 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV70, 8세대)</t>
+          <t>캠리 (XV80, 9세대)</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3623,7 +3607,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -3633,7 +3617,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
@@ -3642,11 +3626,7 @@
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr"/>
-      <c r="L45" s="9" t="inlineStr">
-        <is>
-          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L45" s="9" t="inlineStr"/>
       <c r="M45" s="9" t="inlineStr"/>
       <c r="N45" s="9" t="inlineStr">
         <is>
@@ -3655,7 +3635,7 @@
       </c>
       <c r="O45" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
+          <t>transpondery(Toyota Camry 80 2025–2026 North America NXP HITAG-AES ID4A NCF29A1M(8990H-AQ010 314MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(9세대 2024.11.26 국내 출시)</t>
         </is>
       </c>
       <c r="P45" s="9" t="inlineStr"/>
@@ -3668,12 +3648,12 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV70, 8세대)</t>
+          <t>아발론 (XX50)</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -3701,22 +3681,14 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I46" s="9" t="inlineStr"/>
       <c r="J46" s="9" t="inlineStr">
         <is>
           <t>TOY51</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr"/>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L46" s="9" t="inlineStr"/>
       <c r="M46" s="9" t="inlineStr"/>
       <c r="N46" s="9" t="inlineStr">
         <is>
@@ -3725,7 +3697,7 @@
       </c>
       <c r="O46" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
+          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
         </is>
       </c>
       <c r="P46" s="9" t="inlineStr"/>
@@ -3738,12 +3710,12 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV70, 8세대)</t>
+          <t>아발론 (XX50)</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -3771,22 +3743,14 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I47" s="9" t="inlineStr"/>
       <c r="J47" s="9" t="inlineStr">
         <is>
           <t>TOY51</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr"/>
-      <c r="L47" s="9" t="inlineStr">
-        <is>
-          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L47" s="9" t="inlineStr"/>
       <c r="M47" s="9" t="inlineStr"/>
       <c r="N47" s="9" t="inlineStr">
         <is>
@@ -3795,7 +3759,7 @@
       </c>
       <c r="O47" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
+          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
         </is>
       </c>
       <c r="P47" s="9" t="inlineStr"/>
@@ -3808,12 +3772,12 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV70, 8세대)</t>
+          <t>아발론 (XX50)</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3841,22 +3805,14 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I48" s="9" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
           <t>TOY51</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr"/>
-      <c r="L48" s="9" t="inlineStr">
-        <is>
-          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L48" s="9" t="inlineStr"/>
       <c r="M48" s="9" t="inlineStr"/>
       <c r="N48" s="9" t="inlineStr">
         <is>
@@ -3865,7 +3821,7 @@
       </c>
       <c r="O48" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
+          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
         </is>
       </c>
       <c r="P48" s="9" t="inlineStr"/>
@@ -3878,12 +3834,12 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV70, 8세대)</t>
+          <t>아발론 (XX50)</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3911,22 +3867,14 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I49" s="9" t="inlineStr"/>
       <c r="J49" s="9" t="inlineStr">
         <is>
           <t>TOY51</t>
         </is>
       </c>
       <c r="K49" s="9" t="inlineStr"/>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L49" s="9" t="inlineStr"/>
       <c r="M49" s="9" t="inlineStr"/>
       <c r="N49" s="9" t="inlineStr">
         <is>
@@ -3935,7 +3883,7 @@
       </c>
       <c r="O49" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
+          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
         </is>
       </c>
       <c r="P49" s="9" t="inlineStr"/>
@@ -3948,12 +3896,12 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV70, 8세대)</t>
+          <t>아발론 (XX50)</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>2024(단종)</t>
+          <t>2022(단종)</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3981,22 +3929,14 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I50" s="9" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
           <t>TOY51</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr"/>
-      <c r="L50" s="9" t="inlineStr">
-        <is>
-          <t>89904-33570[해외 공용 품번], 89904-33770[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L50" s="9" t="inlineStr"/>
       <c r="M50" s="9" t="inlineStr"/>
       <c r="N50" s="9" t="inlineStr">
         <is>
@@ -4005,7 +3945,7 @@
       </c>
       <c r="O50" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 2018–2024 Texas H-8A DST-AES A9(89904-06220·06240 315MHz 뺌), TOY51 비상키 69515-47030), abkeys(순정 Camry 2018-2020 유럽·중동 스마트키 89904-33570·89904-33770 433MHz BR2EX P1 A9), 위키백과(8세대 2017.10.19 국내 출시 — 일본산, 9세대 2024.11.26)</t>
+          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
         </is>
       </c>
       <c r="P50" s="9" t="inlineStr"/>
@@ -4018,12 +3958,12 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV80, 9세대)</t>
+          <t>크라운 (크로스오버)</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -4043,7 +3983,7 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -4062,7 +4002,11 @@
         </is>
       </c>
       <c r="K51" s="9" t="inlineStr"/>
-      <c r="L51" s="9" t="inlineStr"/>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>8990H-33022[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M51" s="9" t="inlineStr"/>
       <c r="N51" s="9" t="inlineStr">
         <is>
@@ -4071,7 +4015,7 @@
       </c>
       <c r="O51" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 80 2025–2026 North America NXP HITAG-AES ID4A NCF29A1M(8990H-AQ010 314MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(9세대 2024.11.26 국내 출시)</t>
+          <t>transpondery(Toyota Crown 2023–2026 Texas H-8A DST-AES 스마트키(8990H-30190 315MHz 뺌), 비상키 69515-K0010·69515-K0020), auto-keys.eu(순정 Crown 2023 스마트키 8990H-33022 433MHz 8A), 위키백과(크라운 크로스오버 2023.6.5 국내 출시)</t>
         </is>
       </c>
       <c r="P51" s="9" t="inlineStr"/>
@@ -4084,12 +4028,12 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV80, 9세대)</t>
+          <t>크라운 (크로스오버)</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -4109,7 +4053,7 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -4128,7 +4072,11 @@
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr"/>
-      <c r="L52" s="9" t="inlineStr"/>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>8990H-33022[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M52" s="9" t="inlineStr"/>
       <c r="N52" s="9" t="inlineStr">
         <is>
@@ -4137,7 +4085,7 @@
       </c>
       <c r="O52" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 80 2025–2026 North America NXP HITAG-AES ID4A NCF29A1M(8990H-AQ010 314MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(9세대 2024.11.26 국내 출시)</t>
+          <t>transpondery(Toyota Crown 2023–2026 Texas H-8A DST-AES 스마트키(8990H-30190 315MHz 뺌), 비상키 69515-K0010·69515-K0020), auto-keys.eu(순정 Crown 2023 스마트키 8990H-33022 433MHz 8A), 위키백과(크라운 크로스오버 2023.6.5 국내 출시)</t>
         </is>
       </c>
       <c r="P52" s="9" t="inlineStr"/>
@@ -4150,12 +4098,12 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>캠리 (XV80, 9세대)</t>
+          <t>크라운 (크로스오버)</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -4175,7 +4123,7 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -4194,7 +4142,11 @@
         </is>
       </c>
       <c r="K53" s="9" t="inlineStr"/>
-      <c r="L53" s="9" t="inlineStr"/>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>8990H-33022[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M53" s="9" t="inlineStr"/>
       <c r="N53" s="9" t="inlineStr">
         <is>
@@ -4203,7 +4155,7 @@
       </c>
       <c r="O53" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Camry 80 2025–2026 North America NXP HITAG-AES ID4A NCF29A1M(8990H-AQ010 314MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(9세대 2024.11.26 국내 출시)</t>
+          <t>transpondery(Toyota Crown 2023–2026 Texas H-8A DST-AES 스마트키(8990H-30190 315MHz 뺌), 비상키 69515-K0010·69515-K0020), auto-keys.eu(순정 Crown 2023 스마트키 8990H-33022 433MHz 8A), 위키백과(크라운 크로스오버 2023.6.5 국내 출시)</t>
         </is>
       </c>
       <c r="P53" s="9" t="inlineStr"/>
@@ -4216,12 +4168,12 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>아발론 (XX50)</t>
+          <t>크라운 (크로스오버)</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -4249,14 +4201,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr"/>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
           <t>TOY51</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr"/>
-      <c r="L54" s="9" t="inlineStr"/>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>8990H-33022[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M54" s="9" t="inlineStr"/>
       <c r="N54" s="9" t="inlineStr">
         <is>
@@ -4265,7 +4225,7 @@
       </c>
       <c r="O54" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
+          <t>transpondery(Toyota Crown 2023–2026 Texas H-8A DST-AES 스마트키(8990H-30190 315MHz 뺌), 비상키 69515-K0010·69515-K0020), auto-keys.eu(순정 Crown 2023 스마트키 8990H-33022 433MHz 8A), 위키백과(크라운 크로스오버 2023.6.5 국내 출시)</t>
         </is>
       </c>
       <c r="P54" s="9" t="inlineStr"/>
@@ -4278,12 +4238,12 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>아발론 (XX50)</t>
+          <t>GR 수프라</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -4303,7 +4263,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -4314,20 +4274,24 @@
       <c r="I55" s="9" t="inlineStr"/>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K55" s="9" t="inlineStr"/>
-      <c r="L55" s="9" t="inlineStr"/>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>8990A-WAA12[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M55" s="9" t="inlineStr"/>
       <c r="N55" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O55" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
+          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P55" s="9" t="inlineStr"/>
@@ -4340,12 +4304,12 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>아발론 (XX50)</t>
+          <t>GR 수프라</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -4365,7 +4329,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -4376,20 +4340,24 @@
       <c r="I56" s="9" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K56" s="9" t="inlineStr"/>
-      <c r="L56" s="9" t="inlineStr"/>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>8990A-WAA12[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M56" s="9" t="inlineStr"/>
       <c r="N56" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O56" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
+          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P56" s="9" t="inlineStr"/>
@@ -4402,12 +4370,12 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>아발론 (XX50)</t>
+          <t>GR 수프라</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -4427,7 +4395,7 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -4438,20 +4406,24 @@
       <c r="I57" s="9" t="inlineStr"/>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K57" s="9" t="inlineStr"/>
-      <c r="L57" s="9" t="inlineStr"/>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>8990A-WAA12[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M57" s="9" t="inlineStr"/>
       <c r="N57" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O57" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
+          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P57" s="9" t="inlineStr"/>
@@ -4464,12 +4436,12 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>아발론 (XX50)</t>
+          <t>GR 수프라</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>2022(단종)</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -4489,7 +4461,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -4500,20 +4472,24 @@
       <c r="I58" s="9" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr"/>
-      <c r="L58" s="9" t="inlineStr"/>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>8990A-WAA12[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M58" s="9" t="inlineStr"/>
       <c r="N58" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O58" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Avalon 2018–2022 Texas H-8A DST-AES 8A-AA(8990H-07010·07070 315MHz 뺌)), 위키백과(XX50 2018.11.6 국내 출시, 2022 북미 단종으로 국내 수입 중단·2023.5 크라운 크로스오버가 대체)</t>
+          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P58" s="9" t="inlineStr"/>
@@ -4526,12 +4502,12 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>크라운 (크로스오버)</t>
+          <t>GR 수프라</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -4551,7 +4527,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -4559,31 +4535,27 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I59" s="9" t="inlineStr"/>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K59" s="9" t="inlineStr"/>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>8990H-33022[해외 공용 품번]</t>
+          <t>8990A-WAA12[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr"/>
       <c r="N59" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O59" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Crown 2023–2026 Texas H-8A DST-AES 스마트키(8990H-30190 315MHz 뺌), 비상키 69515-K0010·69515-K0020), auto-keys.eu(순정 Crown 2023 스마트키 8990H-33022 433MHz 8A), 위키백과(크라운 크로스오버 2023.6.5 국내 출시)</t>
+          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P59" s="9" t="inlineStr"/>
@@ -4596,12 +4568,12 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>크라운 (크로스오버)</t>
+          <t>GR 수프라</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -4621,7 +4593,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -4629,31 +4601,27 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr"/>
       <c r="L60" s="9" t="inlineStr">
         <is>
-          <t>8990H-33022[해외 공용 품번]</t>
+          <t>8990A-WAA12[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M60" s="9" t="inlineStr"/>
       <c r="N60" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O60" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Crown 2023–2026 Texas H-8A DST-AES 스마트키(8990H-30190 315MHz 뺌), 비상키 69515-K0010·69515-K0020), auto-keys.eu(순정 Crown 2023 스마트키 8990H-33022 433MHz 8A), 위키백과(크라운 크로스오버 2023.6.5 국내 출시)</t>
+          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P60" s="9" t="inlineStr"/>
@@ -4666,12 +4634,12 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>크라운 (크로스오버)</t>
+          <t>GR 수프라</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -4691,7 +4659,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -4699,31 +4667,27 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I61" s="9" t="inlineStr"/>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr"/>
       <c r="L61" s="9" t="inlineStr">
         <is>
-          <t>8990H-33022[해외 공용 품번]</t>
+          <t>8990A-WAA12[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M61" s="9" t="inlineStr"/>
       <c r="N61" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O61" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Crown 2023–2026 Texas H-8A DST-AES 스마트키(8990H-30190 315MHz 뺌), 비상키 69515-K0010·69515-K0020), auto-keys.eu(순정 Crown 2023 스마트키 8990H-33022 433MHz 8A), 위키백과(크라운 크로스오버 2023.6.5 국내 출시)</t>
+          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P61" s="9" t="inlineStr"/>
@@ -4736,12 +4700,12 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>크라운 (크로스오버)</t>
+          <t>GR86</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -4769,20 +4733,16 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I62" s="9" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>LXP90</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr"/>
       <c r="L62" s="9" t="inlineStr">
         <is>
-          <t>8990H-33022[해외 공용 품번]</t>
+          <t>SU003-10030[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M62" s="9" t="inlineStr"/>
@@ -4793,7 +4753,7 @@
       </c>
       <c r="O62" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Crown 2023–2026 Texas H-8A DST-AES 스마트키(8990H-30190 315MHz 뺌), 비상키 69515-K0010·69515-K0020), auto-keys.eu(순정 Crown 2023 스마트키 8990H-33022 433MHz 8A), 위키백과(크라운 크로스오버 2023.6.5 국내 출시)</t>
+          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), american key supply(GR86 2022-2025 HYQ14AHK 비상키 LXP90), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
         </is>
       </c>
       <c r="P62" s="9" t="inlineStr"/>
@@ -4806,12 +4766,12 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>GR 수프라</t>
+          <t>GR86</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -4831,7 +4791,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -4842,24 +4802,24 @@
       <c r="I63" s="9" t="inlineStr"/>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>LXP90</t>
         </is>
       </c>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr">
         <is>
-          <t>8990A-WAA12[해외 공용 품번]</t>
+          <t>SU003-10030[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M63" s="9" t="inlineStr"/>
       <c r="N63" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O63" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
+          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), american key supply(GR86 2022-2025 HYQ14AHK 비상키 LXP90), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
         </is>
       </c>
       <c r="P63" s="9" t="inlineStr"/>
@@ -4872,12 +4832,12 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>GR 수프라</t>
+          <t>GR86</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -4897,7 +4857,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -4908,24 +4868,24 @@
       <c r="I64" s="9" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>LXP90</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr"/>
       <c r="L64" s="9" t="inlineStr">
         <is>
-          <t>8990A-WAA12[해외 공용 품번]</t>
+          <t>SU003-10030[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M64" s="9" t="inlineStr"/>
       <c r="N64" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O64" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
+          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), american key supply(GR86 2022-2025 HYQ14AHK 비상키 LXP90), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
         </is>
       </c>
       <c r="P64" s="9" t="inlineStr"/>
@@ -4938,12 +4898,12 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>GR 수프라</t>
+          <t>GR86</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -4963,7 +4923,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
@@ -4974,24 +4934,24 @@
       <c r="I65" s="9" t="inlineStr"/>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>LXP90</t>
         </is>
       </c>
       <c r="K65" s="9" t="inlineStr"/>
       <c r="L65" s="9" t="inlineStr">
         <is>
-          <t>8990A-WAA12[해외 공용 품번]</t>
+          <t>SU003-10030[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M65" s="9" t="inlineStr"/>
       <c r="N65" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O65" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
+          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), american key supply(GR86 2022-2025 HYQ14AHK 비상키 LXP90), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
         </is>
       </c>
       <c r="P65" s="9" t="inlineStr"/>
@@ -5004,12 +4964,12 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>GR 수프라</t>
+          <t>GR86</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -5029,7 +4989,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
@@ -5040,24 +5000,24 @@
       <c r="I66" s="9" t="inlineStr"/>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>LXP90</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr"/>
       <c r="L66" s="9" t="inlineStr">
         <is>
-          <t>8990A-WAA12[해외 공용 품번]</t>
+          <t>SU003-10030[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M66" s="9" t="inlineStr"/>
       <c r="N66" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O66" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
+          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), american key supply(GR86 2022-2025 HYQ14AHK 비상키 LXP90), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
         </is>
       </c>
       <c r="P66" s="9" t="inlineStr"/>
@@ -5070,22 +5030,22 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>GR 수프라</t>
+          <t>RAV4 (XA30, 3세대)</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -5095,35 +5055,35 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID72</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I67" s="9" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>89070-42531[리모컨키, 해외 공용 품번], 89070-28812[리모컨키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>TOY43</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr"/>
-      <c r="L67" s="9" t="inlineStr">
-        <is>
-          <t>8990A-WAA12[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L67" s="9" t="inlineStr"/>
       <c r="M67" s="9" t="inlineStr"/>
       <c r="N67" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>이모빌라이저 ECU</t>
         </is>
       </c>
       <c r="O67" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
+          <t>transpondery(Toyota RAV4 2004–2009 Texas 4D-67G, 2010–2012 Texas G DST80 G-Type Key), abkeys(순정 RAV4 2005-2011 유럽·중동 리모컨 일체형 키 89070-42531·89070-28812 433MHz TOY43), 위키백과(RAV4 2009.10 국내 판매, 4세대 2013.5)</t>
         </is>
       </c>
       <c r="P67" s="9" t="inlineStr"/>
@@ -5136,22 +5096,22 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>GR 수프라</t>
+          <t>RAV4 (XA30, 3세대)</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -5161,35 +5121,35 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID72</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I68" s="9" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>89070-42531[리모컨키, 해외 공용 품번], 89070-28812[리모컨키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>TOY43</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>8990A-WAA12[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L68" s="9" t="inlineStr"/>
       <c r="M68" s="9" t="inlineStr"/>
       <c r="N68" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>이모빌라이저 ECU</t>
         </is>
       </c>
       <c r="O68" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
+          <t>transpondery(Toyota RAV4 2004–2009 Texas 4D-67G, 2010–2012 Texas G DST80 G-Type Key), abkeys(순정 RAV4 2005-2011 유럽·중동 리모컨 일체형 키 89070-42531·89070-28812 433MHz TOY43), 위키백과(RAV4 2009.10 국내 판매, 4세대 2013.5)</t>
         </is>
       </c>
       <c r="P68" s="9" t="inlineStr"/>
@@ -5202,22 +5162,22 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>GR 수프라</t>
+          <t>RAV4 (XA30, 3세대)</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -5227,35 +5187,35 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID72</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I69" s="9" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>89070-42531[리모컨키, 해외 공용 품번], 89070-28812[리모컨키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>TOY43</t>
         </is>
       </c>
       <c r="K69" s="9" t="inlineStr"/>
-      <c r="L69" s="9" t="inlineStr">
-        <is>
-          <t>8990A-WAA12[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L69" s="9" t="inlineStr"/>
       <c r="M69" s="9" t="inlineStr"/>
       <c r="N69" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>이모빌라이저 ECU</t>
         </is>
       </c>
       <c r="O69" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR Supra A90·A91 2020–2026 NXP Hitag Pro ID49, BMW BDC, 8990A-WAA12 FCC N5F-ID21A 433MHz, HU100R), 위키백과(GR 수프라 2020.1.21 국내 정식 출시)</t>
+          <t>transpondery(Toyota RAV4 2004–2009 Texas 4D-67G, 2010–2012 Texas G DST80 G-Type Key), abkeys(순정 RAV4 2005-2011 유럽·중동 리모컨 일체형 키 89070-42531·89070-28812 433MHz TOY43), 위키백과(RAV4 2009.10 국내 판매, 4세대 2013.5)</t>
         </is>
       </c>
       <c r="P69" s="9" t="inlineStr"/>
@@ -5268,22 +5228,22 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>GR86</t>
+          <t>RAV4 (XA30, 3세대)</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2012(단종)</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -5293,31 +5253,35 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID72</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>89070-42531[리모컨키, 해외 공용 품번], 89070-28812[리모컨키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>TOY43</t>
+        </is>
+      </c>
       <c r="K70" s="9" t="inlineStr"/>
-      <c r="L70" s="9" t="inlineStr">
-        <is>
-          <t>SU003-10030[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L70" s="9" t="inlineStr"/>
       <c r="M70" s="9" t="inlineStr"/>
       <c r="N70" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>이모빌라이저 ECU</t>
         </is>
       </c>
       <c r="O70" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
+          <t>transpondery(Toyota RAV4 2004–2009 Texas 4D-67G, 2010–2012 Texas G DST80 G-Type Key), abkeys(순정 RAV4 2005-2011 유럽·중동 리모컨 일체형 키 89070-42531·89070-28812 433MHz TOY43), 위키백과(RAV4 2009.10 국내 판매, 4세대 2013.5)</t>
         </is>
       </c>
       <c r="P70" s="9" t="inlineStr"/>
@@ -5330,12 +5294,12 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>GR86</t>
+          <t>RAV4 (XA40, 4세대)</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -5363,12 +5327,20 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr"/>
-      <c r="J71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>TOY51</t>
+        </is>
+      </c>
       <c r="K71" s="9" t="inlineStr"/>
       <c r="L71" s="9" t="inlineStr">
         <is>
-          <t>SU003-10030[해외 공용 품번]</t>
+          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M71" s="9" t="inlineStr"/>
@@ -5379,7 +5351,7 @@
       </c>
       <c r="O71" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
+          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
         </is>
       </c>
       <c r="P71" s="9" t="inlineStr"/>
@@ -5392,12 +5364,12 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>GR86</t>
+          <t>RAV4 (XA40, 4세대)</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -5425,12 +5397,20 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I72" s="9" t="inlineStr"/>
-      <c r="J72" s="9" t="inlineStr"/>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>TOY51</t>
+        </is>
+      </c>
       <c r="K72" s="9" t="inlineStr"/>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>SU003-10030[해외 공용 품번]</t>
+          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M72" s="9" t="inlineStr"/>
@@ -5441,7 +5421,7 @@
       </c>
       <c r="O72" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
+          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
         </is>
       </c>
       <c r="P72" s="9" t="inlineStr"/>
@@ -5454,12 +5434,12 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>GR86</t>
+          <t>RAV4 (XA40, 4세대)</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -5487,12 +5467,20 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I73" s="9" t="inlineStr"/>
-      <c r="J73" s="9" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>TOY51</t>
+        </is>
+      </c>
       <c r="K73" s="9" t="inlineStr"/>
       <c r="L73" s="9" t="inlineStr">
         <is>
-          <t>SU003-10030[해외 공용 품번]</t>
+          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M73" s="9" t="inlineStr"/>
@@ -5503,7 +5491,7 @@
       </c>
       <c r="O73" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
+          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
         </is>
       </c>
       <c r="P73" s="9" t="inlineStr"/>
@@ -5516,12 +5504,12 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>GR86</t>
+          <t>RAV4 (XA40, 4세대)</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -5549,12 +5537,20 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I74" s="9" t="inlineStr"/>
-      <c r="J74" s="9" t="inlineStr"/>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>TOY51</t>
+        </is>
+      </c>
       <c r="K74" s="9" t="inlineStr"/>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>SU003-10030[해외 공용 품번]</t>
+          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M74" s="9" t="inlineStr"/>
@@ -5565,7 +5561,7 @@
       </c>
       <c r="O74" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota GR86 2022–2026 Texas H-8A DST-AES 스바루 계열 스마트키 SU003-10030 FCC HYQ14AHK 433/434MHz), 위키백과(2세대 86 2022.5.16 국내 출시, 6단 수동만)</t>
+          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
         </is>
       </c>
       <c r="P74" s="9" t="inlineStr"/>
@@ -5578,22 +5574,22 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA30, 3세대)</t>
+          <t>RAV4 (XA40, 4세대)</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -5603,35 +5599,39 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>ID72</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>89070-42531[리모컨키, 해외 공용 품번], 89070-28812[리모컨키, 해외 공용 품번]</t>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>TOY43</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr"/>
-      <c r="L75" s="9" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M75" s="9" t="inlineStr"/>
       <c r="N75" s="9" t="inlineStr">
         <is>
-          <t>이모빌라이저 ECU</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O75" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2004–2009 Texas 4D-67G, 2010–2012 Texas G DST80 G-Type Key), abkeys(순정 RAV4 2005-2011 유럽·중동 리모컨 일체형 키 89070-42531·89070-28812 433MHz TOY43), 위키백과(RAV4 2009.10 국내 판매, 4세대 2013.5)</t>
+          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
         </is>
       </c>
       <c r="P75" s="9" t="inlineStr"/>
@@ -5644,22 +5644,22 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA30, 3세대)</t>
+          <t>RAV4 (XA40, 4세대)</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2018(단종)</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -5669,35 +5669,39 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>ID72</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>89070-42531[리모컨키, 해외 공용 품번], 89070-28812[리모컨키, 해외 공용 품번]</t>
+          <t>69515-33100[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>TOY43</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr"/>
-      <c r="L76" s="9" t="inlineStr"/>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M76" s="9" t="inlineStr"/>
       <c r="N76" s="9" t="inlineStr">
         <is>
-          <t>이모빌라이저 ECU</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O76" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2004–2009 Texas 4D-67G, 2010–2012 Texas G DST80 G-Type Key), abkeys(순정 RAV4 2005-2011 유럽·중동 리모컨 일체형 키 89070-42531·89070-28812 433MHz TOY43), 위키백과(RAV4 2009.10 국내 판매, 4세대 2013.5)</t>
+          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
         </is>
       </c>
       <c r="P76" s="9" t="inlineStr"/>
@@ -5710,22 +5714,22 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA30, 3세대)</t>
+          <t>RAV4 (XA50, 5세대)</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -5735,35 +5739,39 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>ID72</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>89070-42531[리모컨키, 해외 공용 품번], 89070-28812[리모컨키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>TOY43</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M77" s="9" t="inlineStr"/>
       <c r="N77" s="9" t="inlineStr">
         <is>
-          <t>이모빌라이저 ECU</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O77" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2004–2009 Texas 4D-67G, 2010–2012 Texas G DST80 G-Type Key), abkeys(순정 RAV4 2005-2011 유럽·중동 리모컨 일체형 키 89070-42531·89070-28812 433MHz TOY43), 위키백과(RAV4 2009.10 국내 판매, 4세대 2013.5)</t>
+          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
         </is>
       </c>
       <c r="P77" s="9" t="inlineStr"/>
@@ -5776,22 +5784,22 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA30, 3세대)</t>
+          <t>RAV4 (XA50, 5세대)</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>2012(단종)</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -5801,35 +5809,39 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>ID72</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>89070-42531[리모컨키, 해외 공용 품번], 89070-28812[리모컨키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>TOY43</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr"/>
-      <c r="L78" s="9" t="inlineStr"/>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M78" s="9" t="inlineStr"/>
       <c r="N78" s="9" t="inlineStr">
         <is>
-          <t>이모빌라이저 ECU</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O78" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2004–2009 Texas 4D-67G, 2010–2012 Texas G DST80 G-Type Key), abkeys(순정 RAV4 2005-2011 유럽·중동 리모컨 일체형 키 89070-42531·89070-28812 433MHz TOY43), 위키백과(RAV4 2009.10 국내 판매, 4세대 2013.5)</t>
+          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
         </is>
       </c>
       <c r="P78" s="9" t="inlineStr"/>
@@ -5842,12 +5854,12 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA40, 4세대)</t>
+          <t>RAV4 (XA50, 5세대)</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -5877,7 +5889,7 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
@@ -5888,7 +5900,7 @@
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr">
         <is>
-          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
+          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M79" s="9" t="inlineStr"/>
@@ -5899,7 +5911,7 @@
       </c>
       <c r="O79" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
+          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
         </is>
       </c>
       <c r="P79" s="9" t="inlineStr"/>
@@ -5912,12 +5924,12 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA40, 4세대)</t>
+          <t>RAV4 (XA50, 5세대)</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -5947,7 +5959,7 @@
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr">
@@ -5958,7 +5970,7 @@
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr">
         <is>
-          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
+          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M80" s="9" t="inlineStr"/>
@@ -5969,7 +5981,7 @@
       </c>
       <c r="O80" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
+          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
         </is>
       </c>
       <c r="P80" s="9" t="inlineStr"/>
@@ -5982,12 +5994,12 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA40, 4세대)</t>
+          <t>RAV4 (XA50, 5세대)</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -6017,7 +6029,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J81" s="9" t="inlineStr">
@@ -6028,7 +6040,7 @@
       <c r="K81" s="9" t="inlineStr"/>
       <c r="L81" s="9" t="inlineStr">
         <is>
-          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
+          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M81" s="9" t="inlineStr"/>
@@ -6039,7 +6051,7 @@
       </c>
       <c r="O81" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
+          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
         </is>
       </c>
       <c r="P81" s="9" t="inlineStr"/>
@@ -6052,12 +6064,12 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA40, 4세대)</t>
+          <t>RAV4 (XA50, 5세대)</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -6087,7 +6099,7 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr">
@@ -6098,7 +6110,7 @@
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr">
         <is>
-          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
+          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M82" s="9" t="inlineStr"/>
@@ -6109,7 +6121,7 @@
       </c>
       <c r="O82" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
+          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
         </is>
       </c>
       <c r="P82" s="9" t="inlineStr"/>
@@ -6122,12 +6134,12 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA40, 4세대)</t>
+          <t>RAV4 (XA50, 5세대)</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2025(단종)</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -6157,7 +6169,7 @@
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
+          <t>69515-47030[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J83" s="9" t="inlineStr">
@@ -6168,7 +6180,7 @@
       <c r="K83" s="9" t="inlineStr"/>
       <c r="L83" s="9" t="inlineStr">
         <is>
-          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
+          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M83" s="9" t="inlineStr"/>
@@ -6179,7 +6191,7 @@
       </c>
       <c r="O83" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
+          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
         </is>
       </c>
       <c r="P83" s="9" t="inlineStr"/>
@@ -6192,12 +6204,12 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA40, 4세대)</t>
+          <t>RAV4 (XA60, 6세대)</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -6217,7 +6229,7 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
@@ -6225,20 +6237,12 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>69515-33100[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>TOY51</t>
-        </is>
-      </c>
+      <c r="I84" s="9" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr"/>
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr">
         <is>
-          <t>89904-42180[해외 공용 품번], 89904-42321[해외 공용 품번], 89904-42130[해외 공용 품번], 89904-42230[해외 공용 품번]</t>
+          <t>8990H-0R510[해외 공용 품번], 8990H-0R320[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M84" s="9" t="inlineStr"/>
@@ -6249,7 +6253,7 @@
       </c>
       <c r="O84" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2013–2018 Texas H-8A DST-AES(89904-0R080 315MHz 뺌), TOY51 비상키 69515-33100), abkeys(순정 RAV4 2013-2017 유럽·중동 스마트키 89904-42180·89904-42321 433MHz BA2EQ P1 88, 89904-42130, 2013-2018 일본형 89904-42230 433MHz), 위키백과(4세대 2013.5 국내 판매, 하이브리드 2016.3, 5세대 2019.5)</t>
+          <t>transpondery(Toyota RAV4 2026 North America NXP HITAG-PRO ID49, 8990H-0R510 FCC HYQ14FNB 433.58/434.42MHz), auto-keys.eu(순정 RAV4 2026 스마트키 8990H-0R320 433MHz ID49), 위키백과(6세대 2026.6.16 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P84" s="9" t="inlineStr"/>
@@ -6262,22 +6266,22 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA50, 5세대)</t>
+          <t>벤자 (AV10, 1세대 후기형)</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -6287,30 +6291,22 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>막대키,스마트키</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr"/>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY43[일반 키], TOY48[비상키]</t>
         </is>
       </c>
       <c r="K85" s="9" t="inlineStr"/>
-      <c r="L85" s="9" t="inlineStr">
-        <is>
-          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L85" s="9" t="inlineStr"/>
       <c r="M85" s="9" t="inlineStr"/>
       <c r="N85" s="9" t="inlineStr">
         <is>
@@ -6319,7 +6315,7 @@
       </c>
       <c r="O85" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
+          <t>transpondery(Toyota Venza 2009–2015 4D-67(전기)·Texas G 4D-72 DST80(후기) 트랜스폰더 키, 스마트키·TOY48 비상키), 락스미스키리스(Venza 2013·2014 스마트키 HYQ14ACX G DST80 — 314MHz라 품번 뺌), 위키백과(2012.11 부분변경 모델 국내 수입)</t>
         </is>
       </c>
       <c r="P85" s="9" t="inlineStr"/>
@@ -6332,22 +6328,22 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA50, 5세대)</t>
+          <t>벤자 (AV10, 1세대 후기형)</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -6357,30 +6353,22 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>막대키,스마트키</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="inlineStr"/>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY43[일반 키], TOY48[비상키]</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr"/>
-      <c r="L86" s="9" t="inlineStr">
-        <is>
-          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L86" s="9" t="inlineStr"/>
       <c r="M86" s="9" t="inlineStr"/>
       <c r="N86" s="9" t="inlineStr">
         <is>
@@ -6389,7 +6377,7 @@
       </c>
       <c r="O86" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
+          <t>transpondery(Toyota Venza 2009–2015 4D-67(전기)·Texas G 4D-72 DST80(후기) 트랜스폰더 키, 스마트키·TOY48 비상키), 락스미스키리스(Venza 2013·2014 스마트키 HYQ14ACX G DST80 — 314MHz라 품번 뺌), 위키백과(2012.11 부분변경 모델 국내 수입)</t>
         </is>
       </c>
       <c r="P86" s="9" t="inlineStr"/>
@@ -6402,22 +6390,22 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA50, 5세대)</t>
+          <t>벤자 (AV10, 1세대 후기형)</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -6427,30 +6415,22 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>막대키,스마트키</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr"/>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY43[일반 키], TOY48[비상키]</t>
         </is>
       </c>
       <c r="K87" s="9" t="inlineStr"/>
-      <c r="L87" s="9" t="inlineStr">
-        <is>
-          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L87" s="9" t="inlineStr"/>
       <c r="M87" s="9" t="inlineStr"/>
       <c r="N87" s="9" t="inlineStr">
         <is>
@@ -6459,7 +6439,7 @@
       </c>
       <c r="O87" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
+          <t>transpondery(Toyota Venza 2009–2015 4D-67(전기)·Texas G 4D-72 DST80(후기) 트랜스폰더 키, 스마트키·TOY48 비상키), 락스미스키리스(Venza 2013·2014 스마트키 HYQ14ACX G DST80 — 314MHz라 품번 뺌), 위키백과(2012.11 부분변경 모델 국내 수입)</t>
         </is>
       </c>
       <c r="P87" s="9" t="inlineStr"/>
@@ -6472,22 +6452,22 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA50, 5세대)</t>
+          <t>벤자 (AV10, 1세대 후기형)</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2015(단종)</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -6497,30 +6477,22 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>막대키,스마트키</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="inlineStr"/>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY43[일반 키], TOY48[비상키]</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr"/>
-      <c r="L88" s="9" t="inlineStr">
-        <is>
-          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L88" s="9" t="inlineStr"/>
       <c r="M88" s="9" t="inlineStr"/>
       <c r="N88" s="9" t="inlineStr">
         <is>
@@ -6529,7 +6501,7 @@
       </c>
       <c r="O88" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
+          <t>transpondery(Toyota Venza 2009–2015 4D-67(전기)·Texas G 4D-72 DST80(후기) 트랜스폰더 키, 스마트키·TOY48 비상키), 락스미스키리스(Venza 2013·2014 스마트키 HYQ14ACX G DST80 — 314MHz라 품번 뺌), 위키백과(2012.11 부분변경 모델 국내 수입)</t>
         </is>
       </c>
       <c r="P88" s="9" t="inlineStr"/>
@@ -6542,22 +6514,22 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA50, 5세대)</t>
+          <t>FJ 크루저</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2014(단종)</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -6567,39 +6539,31 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>ID8A</t>
+          <t>ID72</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr"/>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY43</t>
         </is>
       </c>
       <c r="K89" s="9" t="inlineStr"/>
-      <c r="L89" s="9" t="inlineStr">
-        <is>
-          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L89" s="9" t="inlineStr"/>
       <c r="M89" s="9" t="inlineStr"/>
       <c r="N89" s="9" t="inlineStr">
         <is>
-          <t>스마트키 ECU</t>
+          <t>이모빌라이저 ECU</t>
         </is>
       </c>
       <c r="O89" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
+          <t>transpondery(Toyota FJ Cruiser 2011–2014 Texas G DST80 G-Type Key), 나무위키·오토뷰(2013 서울모터쇼 공개 후 2013.12.24 100대 한정 국내 정식 판매)</t>
         </is>
       </c>
       <c r="P89" s="9" t="inlineStr"/>
@@ -6612,12 +6576,12 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA50, 5세대)</t>
+          <t>하이랜더 (XU70, 4세대)</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -6647,7 +6611,7 @@
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J90" s="9" t="inlineStr">
@@ -6658,7 +6622,7 @@
       <c r="K90" s="9" t="inlineStr"/>
       <c r="L90" s="9" t="inlineStr">
         <is>
-          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
+          <t>8990H-0E200[해외 공용 품번], 8990H-0E070[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M90" s="9" t="inlineStr"/>
@@ -6669,7 +6633,7 @@
       </c>
       <c r="O90" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
+          <t>transpondery(Toyota Highlander 2023–2024 Texas H-8A DST-AES 8A-BA(8990H-0E600 314MHz 뺌), 비상키 69515-33120·69515-K0020), auto-keys.eu(순정 Highlander 2020+ 8990H-0E200 434MHz 8A, 2022+ 8990H-0E070 433MHz 8A), 위키백과(4세대 2023.7.25 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P90" s="9" t="inlineStr"/>
@@ -6682,12 +6646,12 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA50, 5세대)</t>
+          <t>하이랜더 (XU70, 4세대)</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>2025(단종)</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -6717,7 +6681,7 @@
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>69515-47030[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J91" s="9" t="inlineStr">
@@ -6728,7 +6692,7 @@
       <c r="K91" s="9" t="inlineStr"/>
       <c r="L91" s="9" t="inlineStr">
         <is>
-          <t>8990H-42170[해외 공용 품번], 8990H-42340[해외 공용 품번], 8990H-42360[해외 공용 품번]</t>
+          <t>8990H-0E200[해외 공용 품번], 8990H-0E070[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M91" s="9" t="inlineStr"/>
@@ -6739,7 +6703,7 @@
       </c>
       <c r="O91" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 XA50 2018–2025 Texas H-8A DST-AES 8A-AA·BA(8990H-0R030·0R220 314MHz 뺌), 비상키 69515-47030), auto-keys.eu(순정 RAV4 스마트키 8990H-42170·8990H-42340·8990H-42360 433MHz), 위키백과(5세대 2019.5 국내 판매, PHEV 2023.2.21, 6세대 2026.6.16)</t>
+          <t>transpondery(Toyota Highlander 2023–2024 Texas H-8A DST-AES 8A-BA(8990H-0E600 314MHz 뺌), 비상키 69515-33120·69515-K0020), auto-keys.eu(순정 Highlander 2020+ 8990H-0E200 434MHz 8A, 2022+ 8990H-0E070 433MHz 8A), 위키백과(4세대 2023.7.25 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P91" s="9" t="inlineStr"/>
@@ -6752,12 +6716,12 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>RAV4 (XA60, 6세대)</t>
+          <t>하이랜더 (XU70, 4세대)</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -6777,7 +6741,7 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID4A</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
@@ -6785,14 +6749,18 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr"/>
-      <c r="J92" s="9" t="inlineStr"/>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>TOY51</t>
+        </is>
+      </c>
       <c r="K92" s="9" t="inlineStr"/>
-      <c r="L92" s="9" t="inlineStr">
-        <is>
-          <t>8990H-0R510[해외 공용 품번], 8990H-0R320[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L92" s="9" t="inlineStr"/>
       <c r="M92" s="9" t="inlineStr"/>
       <c r="N92" s="9" t="inlineStr">
         <is>
@@ -6801,7 +6769,7 @@
       </c>
       <c r="O92" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota RAV4 2026 North America NXP HITAG-PRO ID49, 8990H-0R510 FCC HYQ14FNB 433.58/434.42MHz), auto-keys.eu(순정 RAV4 2026 스마트키 8990H-0R320 433MHz ID49), 위키백과(6세대 2026.6.16 국내 정식 출시)</t>
+          <t>transpondery(Toyota Highlander 2025–2026 NXP HITAG-AES 4A-BA)</t>
         </is>
       </c>
       <c r="P92" s="9" t="inlineStr"/>
@@ -6814,22 +6782,22 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>벤자 (AV10, 1세대 후기형)</t>
+          <t>하이랜더 (XU70, 4세대)</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -6839,18 +6807,22 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID4A</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
-        </is>
-      </c>
-      <c r="I93" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>TOY43[일반 키], TOY48[비상키]</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr"/>
@@ -6863,7 +6835,7 @@
       </c>
       <c r="O93" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Venza 2009–2015 4D-67(전기)·Texas G 4D-72 DST80(후기) 트랜스폰더 키, 스마트키·TOY48 비상키), 락스미스키리스(Venza 2013·2014 스마트키 HYQ14ACX G DST80 — 314MHz라 품번 뺌), 위키백과(2012.11 부분변경 모델 국내 수입)</t>
+          <t>transpondery(Toyota Highlander 2025–2026 NXP HITAG-AES 4A-BA)</t>
         </is>
       </c>
       <c r="P93" s="9" t="inlineStr"/>
@@ -6876,12 +6848,12 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>벤자 (AV10, 1세대 후기형)</t>
+          <t>시에나 (XL30, 3세대)</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -6899,7 +6871,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G94" s="9" t="inlineStr">
+      <c r="G94" s="4" t="inlineStr">
         <is>
           <t>ID72(TMS37126)</t>
         </is>
@@ -6909,7 +6881,11 @@
           <t>막대키,스마트키</t>
         </is>
       </c>
-      <c r="I94" s="9" t="inlineStr"/>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>69515-08020[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
           <t>TOY43[일반 키], TOY48[비상키]</t>
@@ -6918,17 +6894,21 @@
       <c r="K94" s="9" t="inlineStr"/>
       <c r="L94" s="9" t="inlineStr"/>
       <c r="M94" s="9" t="inlineStr"/>
-      <c r="N94" s="9" t="inlineStr">
+      <c r="N94" s="4" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O94" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Venza 2009–2015 4D-67(전기)·Texas G 4D-72 DST80(후기) 트랜스폰더 키, 스마트키·TOY48 비상키), 락스미스키리스(Venza 2013·2014 스마트키 HYQ14ACX G DST80 — 314MHz라 품번 뺌), 위키백과(2012.11 부분변경 모델 국내 수입)</t>
-        </is>
-      </c>
-      <c r="P94" s="9" t="inlineStr"/>
+          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+        </is>
+      </c>
+      <c r="P94" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
@@ -6938,12 +6918,12 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>벤자 (AV10, 1세대 후기형)</t>
+          <t>시에나 (XL30, 3세대)</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -6961,7 +6941,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G95" s="9" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr">
         <is>
           <t>ID72(TMS37126)</t>
         </is>
@@ -6971,7 +6951,11 @@
           <t>막대키,스마트키</t>
         </is>
       </c>
-      <c r="I95" s="9" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>69515-08020[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
           <t>TOY43[일반 키], TOY48[비상키]</t>
@@ -6980,17 +6964,21 @@
       <c r="K95" s="9" t="inlineStr"/>
       <c r="L95" s="9" t="inlineStr"/>
       <c r="M95" s="9" t="inlineStr"/>
-      <c r="N95" s="9" t="inlineStr">
+      <c r="N95" s="4" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O95" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Venza 2009–2015 4D-67(전기)·Texas G 4D-72 DST80(후기) 트랜스폰더 키, 스마트키·TOY48 비상키), 락스미스키리스(Venza 2013·2014 스마트키 HYQ14ACX G DST80 — 314MHz라 품번 뺌), 위키백과(2012.11 부분변경 모델 국내 수입)</t>
-        </is>
-      </c>
-      <c r="P95" s="9" t="inlineStr"/>
+          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+        </is>
+      </c>
+      <c r="P95" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
@@ -7000,12 +6988,12 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>벤자 (AV10, 1세대 후기형)</t>
+          <t>시에나 (XL30, 3세대)</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>2015(단종)</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -7023,7 +7011,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G96" s="9" t="inlineStr">
+      <c r="G96" s="4" t="inlineStr">
         <is>
           <t>ID72(TMS37126)</t>
         </is>
@@ -7033,7 +7021,11 @@
           <t>막대키,스마트키</t>
         </is>
       </c>
-      <c r="I96" s="9" t="inlineStr"/>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>69515-08020[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
           <t>TOY43[일반 키], TOY48[비상키]</t>
@@ -7042,17 +7034,21 @@
       <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
-      <c r="N96" s="9" t="inlineStr">
+      <c r="N96" s="4" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O96" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Venza 2009–2015 4D-67(전기)·Texas G 4D-72 DST80(후기) 트랜스폰더 키, 스마트키·TOY48 비상키), 락스미스키리스(Venza 2013·2014 스마트키 HYQ14ACX G DST80 — 314MHz라 품번 뺌), 위키백과(2012.11 부분변경 모델 국내 수입)</t>
-        </is>
-      </c>
-      <c r="P96" s="9" t="inlineStr"/>
+          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+        </is>
+      </c>
+      <c r="P96" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
@@ -7062,12 +7058,12 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>FJ 크루저</t>
+          <t>시에나 (XL30, 3세대)</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>2014(단종)</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -7085,36 +7081,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>ID72</t>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I97" s="9" t="inlineStr"/>
+          <t>막대키,스마트키</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>69515-08020[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>TOY43</t>
+          <t>TOY43[일반 키], TOY48[비상키]</t>
         </is>
       </c>
       <c r="K97" s="9" t="inlineStr"/>
       <c r="L97" s="9" t="inlineStr"/>
       <c r="M97" s="9" t="inlineStr"/>
-      <c r="N97" s="9" t="inlineStr">
-        <is>
-          <t>이모빌라이저 ECU</t>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O97" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota FJ Cruiser 2011–2014 Texas G DST80 G-Type Key), 나무위키·오토뷰(2013 서울모터쇼 공개 후 2013.12.24 100대 한정 국내 정식 판매)</t>
-        </is>
-      </c>
-      <c r="P97" s="9" t="inlineStr"/>
+          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+        </is>
+      </c>
+      <c r="P97" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
@@ -7124,22 +7128,22 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>하이랜더 (XU70, 4세대)</t>
+          <t>시에나 (XL30, 3세대)</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -7147,44 +7151,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>ID8A</t>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+          <t>69515-08020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY43[일반 키], TOY48[비상키]</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr"/>
-      <c r="L98" s="9" t="inlineStr">
-        <is>
-          <t>8990H-0E200[해외 공용 품번], 8990H-0E070[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L98" s="9" t="inlineStr"/>
       <c r="M98" s="9" t="inlineStr"/>
-      <c r="N98" s="9" t="inlineStr">
+      <c r="N98" s="4" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O98" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Highlander 2023–2024 Texas H-8A DST-AES 8A-BA(8990H-0E600 314MHz 뺌), 비상키 69515-33120·69515-K0020), auto-keys.eu(순정 Highlander 2020+ 8990H-0E200 434MHz 8A, 2022+ 8990H-0E070 433MHz 8A), 위키백과(4세대 2023.7.25 국내 첫 출시)</t>
-        </is>
-      </c>
-      <c r="P98" s="9" t="inlineStr"/>
+          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+        </is>
+      </c>
+      <c r="P98" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
@@ -7194,22 +7198,22 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>하이랜더 (XU70, 4세대)</t>
+          <t>시에나 (XL30, 3세대)</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -7217,44 +7221,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>ID8A</t>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+          <t>69515-08020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY43[일반 키], TOY48[비상키]</t>
         </is>
       </c>
       <c r="K99" s="9" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr">
-        <is>
-          <t>8990H-0E200[해외 공용 품번], 8990H-0E070[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L99" s="9" t="inlineStr"/>
       <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr">
+      <c r="N99" s="4" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O99" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Highlander 2023–2024 Texas H-8A DST-AES 8A-BA(8990H-0E600 314MHz 뺌), 비상키 69515-33120·69515-K0020), auto-keys.eu(순정 Highlander 2020+ 8990H-0E200 434MHz 8A, 2022+ 8990H-0E070 433MHz 8A), 위키백과(4세대 2023.7.25 국내 첫 출시)</t>
-        </is>
-      </c>
-      <c r="P99" s="9" t="inlineStr"/>
+          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+        </is>
+      </c>
+      <c r="P99" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
@@ -7264,22 +7268,22 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>하이랜더 (XU70, 4세대)</t>
+          <t>시에나 (XL30, 3세대)</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -7287,40 +7291,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>ID4A</t>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+          <t>69515-08020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY43[일반 키], TOY48[비상키]</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr"/>
-      <c r="N100" s="9" t="inlineStr">
+      <c r="N100" s="4" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O100" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Highlander 2025–2026 NXP HITAG-AES 4A-BA)</t>
-        </is>
-      </c>
-      <c r="P100" s="9" t="inlineStr"/>
+          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+        </is>
+      </c>
+      <c r="P100" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
@@ -7330,22 +7338,22 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>하이랜더 (XU70, 4세대)</t>
+          <t>시에나 (XL30, 3세대)</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -7353,40 +7361,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>ID4A</t>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>ID72(TMS37126)</t>
         </is>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
+          <t>69515-08020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>TOY51</t>
+          <t>TOY43[일반 키], TOY48[비상키]</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr"/>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="9" t="inlineStr">
+      <c r="N101" s="4" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O101" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Highlander 2025–2026 NXP HITAG-AES 4A-BA)</t>
-        </is>
-      </c>
-      <c r="P101" s="9" t="inlineStr"/>
+          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
@@ -7401,7 +7413,7 @@
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -7471,7 +7483,7 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2020(단종)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -7536,22 +7548,22 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL30, 3세대)</t>
+          <t>시에나 (XL40, 4세대)</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -7559,44 +7571,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>ID72(TMS37126)</t>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>69515-08020[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>TOY43[일반 키], TOY48[비상키]</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr"/>
       <c r="L104" s="9" t="inlineStr"/>
       <c r="M104" s="9" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="N104" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O104" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
-        </is>
-      </c>
-      <c r="P104" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
@@ -7606,22 +7614,22 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL30, 3세대)</t>
+          <t>시에나 (XL40, 4세대)</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -7629,44 +7637,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>ID72(TMS37126)</t>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>69515-08020[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>TOY43[일반 키], TOY48[비상키]</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
       <c r="M105" s="9" t="inlineStr"/>
-      <c r="N105" s="4" t="inlineStr">
+      <c r="N105" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O105" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
-        </is>
-      </c>
-      <c r="P105" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
@@ -7676,22 +7680,22 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL30, 3세대)</t>
+          <t>시에나 (XL40, 4세대)</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -7699,44 +7703,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>ID72(TMS37126)</t>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>69515-08020[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>TOY43[일반 키], TOY48[비상키]</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K106" s="9" t="inlineStr"/>
       <c r="L106" s="9" t="inlineStr"/>
       <c r="M106" s="9" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr">
+      <c r="N106" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O106" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
-        </is>
-      </c>
-      <c r="P106" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
@@ -7746,22 +7746,22 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL30, 3세대)</t>
+          <t>시에나 (XL40, 4세대)</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -7769,44 +7769,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>ID72(TMS37126)</t>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>69515-08020[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>TOY43[일반 키], TOY48[비상키]</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K107" s="9" t="inlineStr"/>
       <c r="L107" s="9" t="inlineStr"/>
       <c r="M107" s="9" t="inlineStr"/>
-      <c r="N107" s="4" t="inlineStr">
+      <c r="N107" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O107" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
-        </is>
-      </c>
-      <c r="P107" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
@@ -7816,22 +7812,22 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL30, 3세대)</t>
+          <t>시에나 (XL40, 4세대)</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -7839,44 +7835,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>ID72(TMS37126)</t>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>69515-08020[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>TOY43[일반 키], TOY48[비상키]</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr"/>
       <c r="L108" s="9" t="inlineStr"/>
       <c r="M108" s="9" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="N108" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O108" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
-        </is>
-      </c>
-      <c r="P108" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
@@ -7886,22 +7878,22 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL30, 3세대)</t>
+          <t>시에나 (XL40, 4세대)</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -7909,44 +7901,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>ID72(TMS37126)</t>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>69515-08020[비상키, 해외 공용 품번]</t>
+          <t>69515-K0020[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>TOY43[일반 키], TOY48[비상키]</t>
+          <t>TOY51</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr"/>
       <c r="L109" s="9" t="inlineStr"/>
       <c r="M109" s="9" t="inlineStr"/>
-      <c r="N109" s="4" t="inlineStr">
+      <c r="N109" s="9" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O109" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
-        </is>
-      </c>
-      <c r="P109" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
-        </is>
-      </c>
+          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
@@ -7956,22 +7944,22 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL30, 3세대)</t>
+          <t>알파드 (AH40, 4세대)</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -7981,24 +7969,16 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
-        </is>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>69515-08020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J110" s="9" t="inlineStr">
-        <is>
-          <t>TOY43[일반 키], TOY48[비상키]</t>
-        </is>
-      </c>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I110" s="9" t="inlineStr"/>
+      <c r="J110" s="9" t="inlineStr"/>
       <c r="K110" s="9" t="inlineStr"/>
       <c r="L110" s="9" t="inlineStr"/>
       <c r="M110" s="9" t="inlineStr"/>
@@ -8009,12 +7989,12 @@
       </c>
       <c r="O110" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+          <t>transpondery(Alphard는 2006–2014 ID67까지만 수록), KEYDIY·onlyda(Alphard·Vellfire 스마트키 8A Tiris DST AES 433/434MHz), OBDII365(2022년 이후 토요타 신차 8A-BA·4A), 위키백과(4세대 2023.9.18 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+          <t>4세대 전용 칩 자료 없음 — 같은 시기 토요타 8A-BA 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8026,22 +8006,22 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL30, 3세대)</t>
+          <t>알파드 (AH40, 4세대)</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>2020(단종)</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -8051,24 +8031,16 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>ID72(TMS37126)</t>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
-        </is>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>69515-08020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J111" s="9" t="inlineStr">
-        <is>
-          <t>TOY43[일반 키], TOY48[비상키]</t>
-        </is>
-      </c>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr"/>
+      <c r="J111" s="9" t="inlineStr"/>
       <c r="K111" s="9" t="inlineStr"/>
       <c r="L111" s="9" t="inlineStr"/>
       <c r="M111" s="9" t="inlineStr"/>
@@ -8079,12 +8051,12 @@
       </c>
       <c r="O111" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna 2011–2014 G DST80·2016–2019 H-8A 일반 키, Smart Key 2011–2020 89904-08010(315MHz 뺌)·비상키 69515-08020), abkeys·UHS(89904-08010 HYQ14ADR TMS37126 DST-4D Page1 98 — ID74 표기 판매처도 있음), 위키백과(3세대 2011.3 국내 출시, 부분변경 2018.3.19, 4세대 2021.4.13)</t>
+          <t>transpondery(Alphard는 2006–2014 ID67까지만 수록), KEYDIY·onlyda(Alphard·Vellfire 스마트키 8A Tiris DST AES 433/434MHz), OBDII365(2022년 이후 토요타 신차 8A-BA·4A), 위키백과(4세대 2023.9.18 국내 정식 출시)</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>스마트키 칩 자료 상충(Page1 98 DST80, ID74 표기)</t>
+          <t>4세대 전용 칩 자료 없음 — 같은 시기 토요타 8A-BA 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8096,12 +8068,12 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL40, 4세대)</t>
+          <t>알파드 (AH40, 4세대)</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -8119,7 +8091,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G112" s="9" t="inlineStr">
+      <c r="G112" s="4" t="inlineStr">
         <is>
           <t>ID8A</t>
         </is>
@@ -8129,30 +8101,26 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J112" s="9" t="inlineStr">
-        <is>
-          <t>TOY51</t>
-        </is>
-      </c>
+      <c r="I112" s="9" t="inlineStr"/>
+      <c r="J112" s="9" t="inlineStr"/>
       <c r="K112" s="9" t="inlineStr"/>
       <c r="L112" s="9" t="inlineStr"/>
       <c r="M112" s="9" t="inlineStr"/>
-      <c r="N112" s="9" t="inlineStr">
+      <c r="N112" s="4" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O112" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P112" s="9" t="inlineStr"/>
+          <t>transpondery(Alphard는 2006–2014 ID67까지만 수록), KEYDIY·onlyda(Alphard·Vellfire 스마트키 8A Tiris DST AES 433/434MHz), OBDII365(2022년 이후 토요타 신차 8A-BA·4A), 위키백과(4세대 2023.9.18 국내 정식 출시)</t>
+        </is>
+      </c>
+      <c r="P112" s="4" t="inlineStr">
+        <is>
+          <t>4세대 전용 칩 자료 없음 — 같은 시기 토요타 8A-BA 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
@@ -8162,12 +8130,12 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>시에나 (XL40, 4세대)</t>
+          <t>알파드 (AH40, 4세대)</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -8185,7 +8153,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G113" s="9" t="inlineStr">
+      <c r="G113" s="4" t="inlineStr">
         <is>
           <t>ID8A</t>
         </is>
@@ -8195,545 +8163,29 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J113" s="9" t="inlineStr">
-        <is>
-          <t>TOY51</t>
-        </is>
-      </c>
+      <c r="I113" s="9" t="inlineStr"/>
+      <c r="J113" s="9" t="inlineStr"/>
       <c r="K113" s="9" t="inlineStr"/>
       <c r="L113" s="9" t="inlineStr"/>
       <c r="M113" s="9" t="inlineStr"/>
-      <c r="N113" s="9" t="inlineStr">
+      <c r="N113" s="4" t="inlineStr">
         <is>
           <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O113" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P113" s="9" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>토요타</t>
-        </is>
-      </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>시에나 (XL40, 4세대)</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>ID8A</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J114" s="9" t="inlineStr">
-        <is>
-          <t>TOY51</t>
-        </is>
-      </c>
-      <c r="K114" s="9" t="inlineStr"/>
-      <c r="L114" s="9" t="inlineStr"/>
-      <c r="M114" s="9" t="inlineStr"/>
-      <c r="N114" s="9" t="inlineStr">
-        <is>
-          <t>스마트키 ECU</t>
-        </is>
-      </c>
-      <c r="O114" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P114" s="9" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>토요타</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>시에나 (XL40, 4세대)</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>ID8A</t>
-        </is>
-      </c>
-      <c r="H115" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J115" s="9" t="inlineStr">
-        <is>
-          <t>TOY51</t>
-        </is>
-      </c>
-      <c r="K115" s="9" t="inlineStr"/>
-      <c r="L115" s="9" t="inlineStr"/>
-      <c r="M115" s="9" t="inlineStr"/>
-      <c r="N115" s="9" t="inlineStr">
-        <is>
-          <t>스마트키 ECU</t>
-        </is>
-      </c>
-      <c r="O115" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P115" s="9" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>토요타</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>시에나 (XL40, 4세대)</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>ID8A</t>
-        </is>
-      </c>
-      <c r="H116" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I116" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J116" s="9" t="inlineStr">
-        <is>
-          <t>TOY51</t>
-        </is>
-      </c>
-      <c r="K116" s="9" t="inlineStr"/>
-      <c r="L116" s="9" t="inlineStr"/>
-      <c r="M116" s="9" t="inlineStr"/>
-      <c r="N116" s="9" t="inlineStr">
-        <is>
-          <t>스마트키 ECU</t>
-        </is>
-      </c>
-      <c r="O116" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P116" s="9" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>토요타</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>시에나 (XL40, 4세대)</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>ID8A</t>
-        </is>
-      </c>
-      <c r="H117" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I117" s="9" t="inlineStr">
-        <is>
-          <t>69515-K0020[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J117" s="9" t="inlineStr">
-        <is>
-          <t>TOY51</t>
-        </is>
-      </c>
-      <c r="K117" s="9" t="inlineStr"/>
-      <c r="L117" s="9" t="inlineStr"/>
-      <c r="M117" s="9" t="inlineStr"/>
-      <c r="N117" s="9" t="inlineStr">
-        <is>
-          <t>스마트키 ECU</t>
-        </is>
-      </c>
-      <c r="O117" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Toyota Sienna XL40 Hybrid 2020–2026 Texas H-8A DST-AES 8A-BA(8990H-08010 315MHz 뺌), 비상키 69515-33120·69515-K0020), 위키백과(4세대 2021.4.13 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P117" s="9" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>토요타</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>알파드 (AH40, 4세대)</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>ID8A</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I118" s="9" t="inlineStr"/>
-      <c r="J118" s="9" t="inlineStr"/>
-      <c r="K118" s="9" t="inlineStr"/>
-      <c r="L118" s="9" t="inlineStr"/>
-      <c r="M118" s="9" t="inlineStr"/>
-      <c r="N118" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 ECU</t>
-        </is>
-      </c>
-      <c r="O118" s="9" t="inlineStr">
-        <is>
           <t>transpondery(Alphard는 2006–2014 ID67까지만 수록), KEYDIY·onlyda(Alphard·Vellfire 스마트키 8A Tiris DST AES 433/434MHz), OBDII365(2022년 이후 토요타 신차 8A-BA·4A), 위키백과(4세대 2023.9.18 국내 정식 출시)</t>
         </is>
       </c>
-      <c r="P118" s="4" t="inlineStr">
+      <c r="P113" s="4" t="inlineStr">
         <is>
           <t>4세대 전용 칩 자료 없음 — 같은 시기 토요타 8A-BA 기준 추정</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>토요타</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>알파드 (AH40, 4세대)</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t>ID8A</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I119" s="9" t="inlineStr"/>
-      <c r="J119" s="9" t="inlineStr"/>
-      <c r="K119" s="9" t="inlineStr"/>
-      <c r="L119" s="9" t="inlineStr"/>
-      <c r="M119" s="9" t="inlineStr"/>
-      <c r="N119" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 ECU</t>
-        </is>
-      </c>
-      <c r="O119" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Alphard는 2006–2014 ID67까지만 수록), KEYDIY·onlyda(Alphard·Vellfire 스마트키 8A Tiris DST AES 433/434MHz), OBDII365(2022년 이후 토요타 신차 8A-BA·4A), 위키백과(4세대 2023.9.18 국내 정식 출시)</t>
-        </is>
-      </c>
-      <c r="P119" s="4" t="inlineStr">
-        <is>
-          <t>4세대 전용 칩 자료 없음 — 같은 시기 토요타 8A-BA 기준 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>토요타</t>
-        </is>
-      </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>알파드 (AH40, 4세대)</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>ID8A</t>
-        </is>
-      </c>
-      <c r="H120" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I120" s="9" t="inlineStr"/>
-      <c r="J120" s="9" t="inlineStr"/>
-      <c r="K120" s="9" t="inlineStr"/>
-      <c r="L120" s="9" t="inlineStr"/>
-      <c r="M120" s="9" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 ECU</t>
-        </is>
-      </c>
-      <c r="O120" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Alphard는 2006–2014 ID67까지만 수록), KEYDIY·onlyda(Alphard·Vellfire 스마트키 8A Tiris DST AES 433/434MHz), OBDII365(2022년 이후 토요타 신차 8A-BA·4A), 위키백과(4세대 2023.9.18 국내 정식 출시)</t>
-        </is>
-      </c>
-      <c r="P120" s="4" t="inlineStr">
-        <is>
-          <t>4세대 전용 칩 자료 없음 — 같은 시기 토요타 8A-BA 기준 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>토요타</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>알파드 (AH40, 4세대)</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>ID8A</t>
-        </is>
-      </c>
-      <c r="H121" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I121" s="9" t="inlineStr"/>
-      <c r="J121" s="9" t="inlineStr"/>
-      <c r="K121" s="9" t="inlineStr"/>
-      <c r="L121" s="9" t="inlineStr"/>
-      <c r="M121" s="9" t="inlineStr"/>
-      <c r="N121" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 ECU</t>
-        </is>
-      </c>
-      <c r="O121" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Alphard는 2006–2014 ID67까지만 수록), KEYDIY·onlyda(Alphard·Vellfire 스마트키 8A Tiris DST AES 433/434MHz), OBDII365(2022년 이후 토요타 신차 8A-BA·4A), 위키백과(4세대 2023.9.18 국내 정식 출시)</t>
-        </is>
-      </c>
-      <c r="P121" s="4" t="inlineStr">
-        <is>
-          <t>4세대 전용 칩 자료 없음 — 같은 시기 토요타 8A-BA 기준 추정</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P121"/>
+  <autoFilter ref="A1:P113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8843,7 +8295,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>- ID4A: NXP HITAG-AES(코롤라 E210·캠리 9세대·하이랜더 2025~)  |  ID49: NXP Hitag Pro(GR 수프라 — BMW BDC, RAV4 6세대)</t>
+          <t>- ID4A: NXP HITAG-AES(캠리 9세대·하이랜더 2025~)  |  ID49: NXP Hitag Pro(GR 수프라 — BMW BDC, RAV4 6세대)</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8326,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>- 주황색: 추정이거나 자료가 서로 다른 값, 또는 국내 정식 판매 이력이 없는 모델(해외 사양 기준).</t>
+          <t>- 주황색: 추정이거나 자료가 서로 다른 값.</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8343,7 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>- 프리우스 C: 2018.5.14 국내 판매 시작, 판매 부진으로 수입 중단 → 2018~2019 / 코롤라 E140: 2011 국내 판매 개시, 2014년 초 수입 중단 → 2011~2013 / 코롤라 E210: 국내 미수입 — 목록 연식대로 남기고 주황색.</t>
+          <t>- 프리우스 C: 2018.5.14 국내 판매 시작, 판매 부진으로 수입 중단 → 2018~2019 / 코롤라 E140: 2011 국내 판매 개시, 2014년 초 수입 중단 → 2011~2013 / 코롤라 E210(목록 2019-현재): 국내 미수입이라 뺐습니다.</t>
         </is>
       </c>
     </row>
